--- a/Lessons_and_Logs/Neural_Networks/Chapter_1/Notes/Chapter_1_Data.xlsx
+++ b/Lessons_and_Logs/Neural_Networks/Chapter_1/Notes/Chapter_1_Data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99d2d0efc5e421e1/Working_Files/Code/Repositories/Python/Lessons_and_Logs/Neural_Networks/Chapter_1/Notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC1048B0395B70645BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37D5DFB8-738E-4363-8432-B41E266474C1}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_F25DC773A252ABDACC1048B0395B70645BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C047C04-7FA9-4FCC-A773-EB3B9DF05234}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="30 Epochs 30 Hidden Nodes" sheetId="1" r:id="rId1"/>
+    <sheet name="30 Epochs 30 Hidden Neurons" sheetId="1" r:id="rId1"/>
+    <sheet name="30 Epochs 100 Hidden Neurons" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="443">
   <si>
     <t>Epoch 0: 9095 / 10000</t>
   </si>
@@ -681,6 +682,690 @@
   </si>
   <si>
     <t>Epoch 29: 9504 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 9003 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9213 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 9307 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9359 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9364 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 9420 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9381 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 9423 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9437 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9420 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 9435 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9451 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9449 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9461 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9463 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9480 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9475 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9476 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9461 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9486 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9482 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9500 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9480 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9453 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9499 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9519 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9514 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9473 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 7918 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9184 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9324 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9378 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 9394 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9390 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9412 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9421 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9452 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 9455 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9479 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9463 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9473 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9499 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9499 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9492 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9507 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9505 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9501 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9507 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9505 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9523 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9491 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9467 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9475 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9534 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 9057 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9228 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 9290 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9365 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9359 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9369 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 9426 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9414 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9418 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9466 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 9428 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9480 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9480 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9461 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9482 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9506 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9487 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9492 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9462 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9496 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9530 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9504 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9496 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9513 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9517 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9512 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 9090 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9236 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 9322 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9381 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9409 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9427 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 9427 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9441 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9458 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 9450 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9465 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9478 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9479 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9498 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9479 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9472 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9498 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9484 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9485 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9495 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9473 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9484 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9466 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9502 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9494 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9495 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 7419 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 7543 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 7632 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 7664 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 7683 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 7690 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 7711 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 7705 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 7717 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 7738 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 7730 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 7730 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 7743 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 7740 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 7753 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 7742 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 7766 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 7762 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 7763 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 7764 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 7766 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 7771 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 7776 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 7775 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 7785 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 7783 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 7786 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 7781 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 7784 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 7787 / 10000</t>
+  </si>
+  <si>
+    <t>net.SGD(training_data, 30, 10, 3.0, test_data=test_data)</t>
+  </si>
+  <si>
+    <t>net.SGD(training_data, 30, 10, 6.0, test_data=test_data)</t>
+  </si>
+  <si>
+    <t>Epoch 0: 6325 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 6495 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 7405 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 7435 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 7486 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 7484 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 7568 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 8644 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 8671 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 8650 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 8692 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 8685 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 8716 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 8712 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 8704 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 8721 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 8735 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 8749 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 8746 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 8752 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 8744 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 8753 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 8755 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 8767 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 8764 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 8774 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 8789 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 8769 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 8790 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 8774 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 7468 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9283 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 9418 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9460 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9491 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 9542 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9551 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 9549 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9597 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9567 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 9585 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9619 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 9613 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9625 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9610 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9630 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9639 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9627 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9628 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9647 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9671 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9655 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9661 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9646 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9653 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9656 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9658 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9660 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9643 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9659 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 9081 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9202 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 9407 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9474 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9532 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 9506 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9555 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 9523 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9558 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9535 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 9583 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9584 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 9590 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9623 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9603 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9624 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9622 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9637 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9647 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9665 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9638 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9639 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9638 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9626 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9632 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9658 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9669 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9656 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9663 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9649 / 10000</t>
   </si>
 </sst>
 </file>
@@ -1067,6 +1752,18 @@
       <c r="H2" t="s">
         <v>186</v>
       </c>
+      <c r="I2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K2" t="s">
+        <v>269</v>
+      </c>
+      <c r="L2" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3">
@@ -1090,6 +1787,18 @@
       <c r="H3" t="s">
         <v>187</v>
       </c>
+      <c r="I3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K3" t="s">
+        <v>270</v>
+      </c>
+      <c r="L3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4">
@@ -1113,6 +1822,18 @@
       <c r="H4" t="s">
         <v>188</v>
       </c>
+      <c r="I4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" t="s">
+        <v>271</v>
+      </c>
+      <c r="L4" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5">
@@ -1136,6 +1857,18 @@
       <c r="H5" t="s">
         <v>189</v>
       </c>
+      <c r="I5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" t="s">
+        <v>245</v>
+      </c>
+      <c r="K5" t="s">
+        <v>272</v>
+      </c>
+      <c r="L5" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6">
@@ -1159,6 +1892,18 @@
       <c r="H6" t="s">
         <v>190</v>
       </c>
+      <c r="I6" t="s">
+        <v>219</v>
+      </c>
+      <c r="J6" t="s">
+        <v>246</v>
+      </c>
+      <c r="K6" t="s">
+        <v>273</v>
+      </c>
+      <c r="L6" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7">
@@ -1182,6 +1927,18 @@
       <c r="H7" t="s">
         <v>191</v>
       </c>
+      <c r="I7" t="s">
+        <v>220</v>
+      </c>
+      <c r="J7" t="s">
+        <v>247</v>
+      </c>
+      <c r="K7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8">
@@ -1205,6 +1962,18 @@
       <c r="H8" t="s">
         <v>104</v>
       </c>
+      <c r="I8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J8" t="s">
+        <v>248</v>
+      </c>
+      <c r="K8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L8" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9">
@@ -1228,6 +1997,18 @@
       <c r="H9" t="s">
         <v>192</v>
       </c>
+      <c r="I9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J9" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10">
@@ -1251,6 +2032,18 @@
       <c r="H10" t="s">
         <v>193</v>
       </c>
+      <c r="I10" t="s">
+        <v>223</v>
+      </c>
+      <c r="J10" t="s">
+        <v>249</v>
+      </c>
+      <c r="K10" t="s">
+        <v>276</v>
+      </c>
+      <c r="L10" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11">
@@ -1274,6 +2067,18 @@
       <c r="H11" t="s">
         <v>194</v>
       </c>
+      <c r="I11" t="s">
+        <v>224</v>
+      </c>
+      <c r="J11" t="s">
+        <v>250</v>
+      </c>
+      <c r="K11" t="s">
+        <v>277</v>
+      </c>
+      <c r="L11" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12">
@@ -1297,6 +2102,18 @@
       <c r="H12" t="s">
         <v>195</v>
       </c>
+      <c r="I12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" t="s">
+        <v>166</v>
+      </c>
+      <c r="L12" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13">
@@ -1320,6 +2137,18 @@
       <c r="H13" t="s">
         <v>196</v>
       </c>
+      <c r="I13" t="s">
+        <v>226</v>
+      </c>
+      <c r="J13" t="s">
+        <v>251</v>
+      </c>
+      <c r="K13" t="s">
+        <v>278</v>
+      </c>
+      <c r="L13" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14">
@@ -1343,6 +2172,18 @@
       <c r="H14" t="s">
         <v>197</v>
       </c>
+      <c r="I14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" t="s">
+        <v>252</v>
+      </c>
+      <c r="K14" t="s">
+        <v>279</v>
+      </c>
+      <c r="L14" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15">
@@ -1366,6 +2207,18 @@
       <c r="H15" t="s">
         <v>198</v>
       </c>
+      <c r="I15" t="s">
+        <v>227</v>
+      </c>
+      <c r="J15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16">
@@ -1389,8 +2242,20 @@
       <c r="H16" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>228</v>
+      </c>
+      <c r="J16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K16" t="s">
+        <v>280</v>
+      </c>
+      <c r="L16" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>15</v>
       </c>
@@ -1412,8 +2277,20 @@
       <c r="H17" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>229</v>
+      </c>
+      <c r="J17" t="s">
+        <v>255</v>
+      </c>
+      <c r="K17" t="s">
+        <v>281</v>
+      </c>
+      <c r="L17" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>16</v>
       </c>
@@ -1435,8 +2312,20 @@
       <c r="H18" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>230</v>
+      </c>
+      <c r="J18" t="s">
+        <v>256</v>
+      </c>
+      <c r="K18" t="s">
+        <v>282</v>
+      </c>
+      <c r="L18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>17</v>
       </c>
@@ -1458,8 +2347,20 @@
       <c r="H19" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>231</v>
+      </c>
+      <c r="J19" t="s">
+        <v>257</v>
+      </c>
+      <c r="K19" t="s">
+        <v>283</v>
+      </c>
+      <c r="L19" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>18</v>
       </c>
@@ -1481,8 +2382,20 @@
       <c r="H20" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>232</v>
+      </c>
+      <c r="J20" t="s">
+        <v>258</v>
+      </c>
+      <c r="K20" t="s">
+        <v>284</v>
+      </c>
+      <c r="L20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>19</v>
       </c>
@@ -1504,8 +2417,20 @@
       <c r="H21" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>233</v>
+      </c>
+      <c r="J21" t="s">
+        <v>259</v>
+      </c>
+      <c r="K21" t="s">
+        <v>285</v>
+      </c>
+      <c r="L21" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>20</v>
       </c>
@@ -1527,8 +2452,20 @@
       <c r="H22" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J22" t="s">
+        <v>260</v>
+      </c>
+      <c r="K22" t="s">
+        <v>286</v>
+      </c>
+      <c r="L22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>21</v>
       </c>
@@ -1550,8 +2487,20 @@
       <c r="H23" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J23" t="s">
+        <v>261</v>
+      </c>
+      <c r="K23" t="s">
+        <v>287</v>
+      </c>
+      <c r="L23" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>22</v>
       </c>
@@ -1573,8 +2522,20 @@
       <c r="H24" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>148</v>
+      </c>
+      <c r="J24" t="s">
+        <v>262</v>
+      </c>
+      <c r="K24" t="s">
+        <v>288</v>
+      </c>
+      <c r="L24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>23</v>
       </c>
@@ -1596,8 +2557,20 @@
       <c r="H25" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>236</v>
+      </c>
+      <c r="J25" t="s">
+        <v>263</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>24</v>
       </c>
@@ -1619,8 +2592,20 @@
       <c r="H26" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>237</v>
+      </c>
+      <c r="J26" t="s">
+        <v>264</v>
+      </c>
+      <c r="K26" t="s">
+        <v>289</v>
+      </c>
+      <c r="L26" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>25</v>
       </c>
@@ -1642,8 +2627,20 @@
       <c r="H27" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" t="s">
+        <v>265</v>
+      </c>
+      <c r="K27" t="s">
+        <v>290</v>
+      </c>
+      <c r="L27" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>26</v>
       </c>
@@ -1665,8 +2662,20 @@
       <c r="H28" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I28" t="s">
+        <v>239</v>
+      </c>
+      <c r="J28" t="s">
+        <v>266</v>
+      </c>
+      <c r="K28" t="s">
+        <v>291</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>27</v>
       </c>
@@ -1688,8 +2697,20 @@
       <c r="H29" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" t="s">
+        <v>240</v>
+      </c>
+      <c r="J29" t="s">
+        <v>267</v>
+      </c>
+      <c r="K29" t="s">
+        <v>292</v>
+      </c>
+      <c r="L29" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>28</v>
       </c>
@@ -1711,8 +2732,20 @@
       <c r="H30" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>241</v>
+      </c>
+      <c r="J30" t="s">
+        <v>183</v>
+      </c>
+      <c r="K30" t="s">
+        <v>293</v>
+      </c>
+      <c r="L30" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>29</v>
       </c>
@@ -1733,6 +2766,18 @@
       </c>
       <c r="H31" t="s">
         <v>214</v>
+      </c>
+      <c r="I31" t="s">
+        <v>242</v>
+      </c>
+      <c r="J31" t="s">
+        <v>268</v>
+      </c>
+      <c r="K31" t="s">
+        <v>294</v>
+      </c>
+      <c r="L31" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
@@ -1883,6 +2928,557 @@
     <row r="62" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D62" t="s">
         <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B609DA57-4304-46EB-8B8F-CE3F33BB4214}">
+  <dimension ref="C1:H32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="5" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="9" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" t="s">
+        <v>384</v>
+      </c>
+      <c r="H4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" t="s">
+        <v>386</v>
+      </c>
+      <c r="H6" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>325</v>
+      </c>
+      <c r="E7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>326</v>
+      </c>
+      <c r="E8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G8" t="s">
+        <v>388</v>
+      </c>
+      <c r="H8" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" t="s">
+        <v>389</v>
+      </c>
+      <c r="H9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>328</v>
+      </c>
+      <c r="E10" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H10" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" t="s">
+        <v>361</v>
+      </c>
+      <c r="G11" t="s">
+        <v>391</v>
+      </c>
+      <c r="H11" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E12" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" t="s">
+        <v>392</v>
+      </c>
+      <c r="H12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" t="s">
+        <v>363</v>
+      </c>
+      <c r="G13" t="s">
+        <v>393</v>
+      </c>
+      <c r="H13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C14">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" t="s">
+        <v>364</v>
+      </c>
+      <c r="G14" t="s">
+        <v>394</v>
+      </c>
+      <c r="H14" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" t="s">
+        <v>365</v>
+      </c>
+      <c r="G15" t="s">
+        <v>395</v>
+      </c>
+      <c r="H15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E16" t="s">
+        <v>366</v>
+      </c>
+      <c r="G16" t="s">
+        <v>396</v>
+      </c>
+      <c r="H16" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>335</v>
+      </c>
+      <c r="E17" t="s">
+        <v>367</v>
+      </c>
+      <c r="G17" t="s">
+        <v>397</v>
+      </c>
+      <c r="H17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>336</v>
+      </c>
+      <c r="E18" t="s">
+        <v>368</v>
+      </c>
+      <c r="G18" t="s">
+        <v>398</v>
+      </c>
+      <c r="H18" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>337</v>
+      </c>
+      <c r="E19" t="s">
+        <v>369</v>
+      </c>
+      <c r="G19" t="s">
+        <v>399</v>
+      </c>
+      <c r="H19" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E20" t="s">
+        <v>370</v>
+      </c>
+      <c r="G20" t="s">
+        <v>400</v>
+      </c>
+      <c r="H20" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
+        <v>339</v>
+      </c>
+      <c r="E21" t="s">
+        <v>371</v>
+      </c>
+      <c r="G21" t="s">
+        <v>401</v>
+      </c>
+      <c r="H21" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>372</v>
+      </c>
+      <c r="G22" t="s">
+        <v>402</v>
+      </c>
+      <c r="H22" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>341</v>
+      </c>
+      <c r="E23" t="s">
+        <v>373</v>
+      </c>
+      <c r="G23" t="s">
+        <v>403</v>
+      </c>
+      <c r="H23" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" t="s">
+        <v>374</v>
+      </c>
+      <c r="G24" t="s">
+        <v>404</v>
+      </c>
+      <c r="H24" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>343</v>
+      </c>
+      <c r="E25" t="s">
+        <v>375</v>
+      </c>
+      <c r="G25" t="s">
+        <v>405</v>
+      </c>
+      <c r="H25" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>344</v>
+      </c>
+      <c r="E26" t="s">
+        <v>376</v>
+      </c>
+      <c r="G26" t="s">
+        <v>406</v>
+      </c>
+      <c r="H26" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>345</v>
+      </c>
+      <c r="E27" t="s">
+        <v>377</v>
+      </c>
+      <c r="G27" t="s">
+        <v>407</v>
+      </c>
+      <c r="H27" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C28">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E28" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" t="s">
+        <v>408</v>
+      </c>
+      <c r="H28" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29" t="s">
+        <v>347</v>
+      </c>
+      <c r="E29" t="s">
+        <v>379</v>
+      </c>
+      <c r="G29" t="s">
+        <v>409</v>
+      </c>
+      <c r="H29" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C30">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>348</v>
+      </c>
+      <c r="E30" t="s">
+        <v>380</v>
+      </c>
+      <c r="G30" t="s">
+        <v>410</v>
+      </c>
+      <c r="H30" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C31">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
+        <v>349</v>
+      </c>
+      <c r="E31" t="s">
+        <v>381</v>
+      </c>
+      <c r="G31" t="s">
+        <v>411</v>
+      </c>
+      <c r="H31" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>350</v>
+      </c>
+      <c r="E32" t="s">
+        <v>382</v>
+      </c>
+      <c r="G32" t="s">
+        <v>412</v>
+      </c>
+      <c r="H32" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/Lessons_and_Logs/Neural_Networks/Chapter_1/Notes/Chapter_1_Data.xlsx
+++ b/Lessons_and_Logs/Neural_Networks/Chapter_1/Notes/Chapter_1_Data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99d2d0efc5e421e1/Working_Files/Code/Repositories/Python/Lessons_and_Logs/Neural_Networks/Chapter_1/Notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_F25DC773A252ABDACC1048B0395B70645BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C047C04-7FA9-4FCC-A773-EB3B9DF05234}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="11_F25DC773A252ABDACC1048B0395B70645BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D4F057D-7EB4-483C-92E9-D6F39D7BE04F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30 Epochs 30 Hidden Neurons" sheetId="1" r:id="rId1"/>
     <sheet name="30 Epochs 100 Hidden Neurons" sheetId="2" r:id="rId2"/>
+    <sheet name="30 Epochs NO Hidden Neurons" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="689">
   <si>
     <t>Epoch 0: 9095 / 10000</t>
   </si>
@@ -1366,13 +1367,899 @@
   </si>
   <si>
     <t>Epoch 29: 9649 / 10000</t>
+  </si>
+  <si>
+    <r>
+      <t>net</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">SGD(training_data, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0.001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>, test_data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>test_data)</t>
+    </r>
+  </si>
+  <si>
+    <t>Epoch 0: 1010 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 1007 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 1008 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 1008 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 986 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 1050 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 1149 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 1209 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 1273 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 1321 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 1363 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 1407 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 1470 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 1533 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 1605 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 1681 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 1748 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 1798 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 1838 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 1874 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 1915 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 1951 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 1987 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 2028 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 2050 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 2079 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 2112 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 2142 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 2163 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 2184 / 10000</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">net </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> network</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Network([</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>784</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>])</t>
+    </r>
+  </si>
+  <si>
+    <t>Epoch 0: 8099 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 9063 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 9068 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 9111 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 9025 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 9105 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 9145 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 9155 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 9145 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 9143 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 9136 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9147 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 9150 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9144 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9158 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9157 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9132 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9163 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9157 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9155 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9156 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9157 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9141 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9129 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9170 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9171 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9153 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9173 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9176 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9165 / 10000</t>
+  </si>
+  <si>
+    <t>net.SGD(training_data, 30, 10,25.0, test_data=test_data)</t>
+  </si>
+  <si>
+    <t>Epoch 0: 5870 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 6563 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 6647 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 6670 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 6675 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 6690 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 6698 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 6723 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 6698 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 6747 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 7482 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 7496 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 7546 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 7495 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 7524 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 7523 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 7528 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 7546 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 7560 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 7541 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 7525 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 7538 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 7552 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 7551 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 7515 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 7575 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 7530 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 7566 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 7553 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 7541 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 7410 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 7472 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 8286 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 8365 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 8410 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 8392 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 8396 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 8379 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 8451 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 8465 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 8511 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 9101 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 9081 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 9129 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 9161 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 9123 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 9151 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 9142 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 9148 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 9138 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 9148 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 9163 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 9156 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 9159 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 9159 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 9156 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 9137 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 9104 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 9152 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 9143 / 10000</t>
+  </si>
+  <si>
+    <t>net.SGD(training_data, 30, 10, 10.0, test_data=test_data)</t>
+  </si>
+  <si>
+    <t>Epoch 0: 5512 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 6414 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 6532 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 6566 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 6631 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 6643 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 6671 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 6652 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 6602 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 6674 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 6691 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 6702 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 6693 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 6717 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 6690 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 6748 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 6743 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 6780 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 6724 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 6679 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 6703 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 6718 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 6708 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 6738 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 6747 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 6800 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 6721 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 6788 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 6779 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 6772 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 6630 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 6770 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 7024 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 6985 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 7000 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 7476 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 7769 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 7764 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 7606 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 7775 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 7793 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 7825 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 7685 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 7813 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 7773 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 7900 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 7809 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 7909 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 7892 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 7899 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 8010 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 7899 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 7834 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 7992 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 7840 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 7897 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 7899 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 7947 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 7951 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 7947 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 4342 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 4484 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 5120 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 5234 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 6159 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 6167 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 6149 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 6224 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 6287 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 6327 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 7099 / 10000</t>
+  </si>
+  <si>
+    <t>network.py:137: RuntimeWarning: overflow encountered in exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  return 1.0/(1.0+np.exp(-z))</t>
+  </si>
+  <si>
+    <t>Epoch 11: 7145 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 7126 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 7110 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 7142 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 7160 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 7150 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 7110 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 7159 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 7158 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 7238 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 7223 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 7118 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 7183 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 7171 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 7216 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 7196 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 7165 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 7177 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 7132 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 0: 6771 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 1: 7182 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 2: 7315 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 3: 7207 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 4: 7375 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 5: 7324 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 6: 7303 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 7: 7415 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 8: 7390 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 9: 7417 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 10: 7456 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 11: 7455 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 12: 7431 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 13: 7444 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 14: 7508 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 15: 7542 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 16: 7531 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 17: 7555 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 18: 7605 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 19: 7547 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 20: 7585 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 21: 7521 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 22: 7579 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 23: 7541 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 24: 7583 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 25: 7782 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 26: 8246 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 27: 8607 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 28: 8971 / 10000</t>
+  </si>
+  <si>
+    <t>Epoch 29: 8969 / 10000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1385,6 +2272,16 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1407,8 +2304,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1424,6 +2327,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1690,12 +2597,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="12" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12">
       <c r="B1" t="s">
         <v>185</v>
       </c>
@@ -1730,7 +2637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12">
       <c r="B2">
         <v>0</v>
       </c>
@@ -1765,7 +2672,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12">
       <c r="B3">
         <v>1</v>
       </c>
@@ -1800,7 +2707,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12">
       <c r="B4">
         <v>2</v>
       </c>
@@ -1835,7 +2742,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1870,7 +2777,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1905,7 +2812,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1940,7 +2847,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1975,7 +2882,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12">
       <c r="B9">
         <v>7</v>
       </c>
@@ -2010,7 +2917,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12">
       <c r="B10">
         <v>8</v>
       </c>
@@ -2045,7 +2952,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12">
       <c r="B11">
         <v>9</v>
       </c>
@@ -2080,7 +2987,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12">
       <c r="B12">
         <v>10</v>
       </c>
@@ -2115,7 +3022,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12">
       <c r="B13">
         <v>11</v>
       </c>
@@ -2150,7 +3057,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12">
       <c r="B14">
         <v>12</v>
       </c>
@@ -2185,7 +3092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12">
       <c r="B15">
         <v>13</v>
       </c>
@@ -2220,7 +3127,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12">
       <c r="B16">
         <v>14</v>
       </c>
@@ -2255,7 +3162,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12">
       <c r="B17">
         <v>15</v>
       </c>
@@ -2290,7 +3197,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12">
       <c r="B18">
         <v>16</v>
       </c>
@@ -2325,7 +3232,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12">
       <c r="B19">
         <v>17</v>
       </c>
@@ -2360,7 +3267,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12">
       <c r="B20">
         <v>18</v>
       </c>
@@ -2395,7 +3302,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12">
       <c r="B21">
         <v>19</v>
       </c>
@@ -2430,7 +3337,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12">
       <c r="B22">
         <v>20</v>
       </c>
@@ -2465,7 +3372,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12">
       <c r="B23">
         <v>21</v>
       </c>
@@ -2500,7 +3407,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12">
       <c r="B24">
         <v>22</v>
       </c>
@@ -2535,7 +3442,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12">
       <c r="B25">
         <v>23</v>
       </c>
@@ -2570,7 +3477,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12">
       <c r="B26">
         <v>24</v>
       </c>
@@ -2605,7 +3512,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12">
       <c r="B27">
         <v>25</v>
       </c>
@@ -2640,7 +3547,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12">
       <c r="B28">
         <v>26</v>
       </c>
@@ -2675,7 +3582,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12">
       <c r="B29">
         <v>27</v>
       </c>
@@ -2710,7 +3617,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12">
       <c r="B30">
         <v>28</v>
       </c>
@@ -2745,7 +3652,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12">
       <c r="B31">
         <v>29</v>
       </c>
@@ -2780,152 +3687,152 @@
         <v>320</v>
       </c>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:4">
       <c r="D33" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:4">
       <c r="D34" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:4">
       <c r="D35" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:4">
       <c r="D36" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:4">
       <c r="D37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:4">
       <c r="D38" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:4">
       <c r="D39" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:4">
       <c r="D40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:4">
       <c r="D41" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:4">
       <c r="D42" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:4">
       <c r="D43" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:4">
       <c r="D44" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:4">
       <c r="D45" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:4">
       <c r="D46" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:4">
       <c r="D47" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:4">
       <c r="D48" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:4">
       <c r="D49" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:4">
       <c r="D50" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:4">
       <c r="D51" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:4">
       <c r="D52" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:4">
       <c r="D53" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:4">
       <c r="D54" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:4">
       <c r="D55" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:4">
       <c r="D56" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:4">
       <c r="D57" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:4">
       <c r="D58" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:4">
       <c r="D59" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:4">
       <c r="D60" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:4">
       <c r="D61" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:4">
       <c r="D62" t="s">
         <v>97</v>
       </c>
@@ -2938,23 +3845,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B609DA57-4304-46EB-8B8F-CE3F33BB4214}">
-  <dimension ref="C1:H32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:J32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="5" width="25.7109375" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" customWidth="1"/>
-    <col min="7" max="9" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" customWidth="1"/>
+    <col min="7" max="8" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:10">
       <c r="D1" t="s">
         <v>351</v>
       </c>
       <c r="G1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="2" spans="3:10">
       <c r="C2" t="s">
         <v>185</v>
       </c>
@@ -2970,8 +3882,11 @@
       <c r="H2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="3:10">
       <c r="C3">
         <v>0</v>
       </c>
@@ -2987,8 +3902,11 @@
       <c r="H3" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10">
       <c r="C4">
         <v>1</v>
       </c>
@@ -3004,8 +3922,11 @@
       <c r="H4" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10">
       <c r="C5">
         <v>2</v>
       </c>
@@ -3021,8 +3942,11 @@
       <c r="H5" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10">
       <c r="C6">
         <v>3</v>
       </c>
@@ -3038,8 +3962,11 @@
       <c r="H6" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10">
       <c r="C7">
         <v>4</v>
       </c>
@@ -3055,8 +3982,11 @@
       <c r="H7" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10">
       <c r="C8">
         <v>5</v>
       </c>
@@ -3072,8 +4002,11 @@
       <c r="H8" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10">
       <c r="C9">
         <v>6</v>
       </c>
@@ -3089,8 +4022,11 @@
       <c r="H9" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10">
       <c r="C10">
         <v>7</v>
       </c>
@@ -3106,8 +4042,11 @@
       <c r="H10" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10">
       <c r="C11">
         <v>8</v>
       </c>
@@ -3123,8 +4062,11 @@
       <c r="H11" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10">
       <c r="C12">
         <v>9</v>
       </c>
@@ -3140,8 +4082,11 @@
       <c r="H12" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10">
       <c r="C13">
         <v>10</v>
       </c>
@@ -3157,8 +4102,11 @@
       <c r="H13" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10">
       <c r="C14">
         <v>11</v>
       </c>
@@ -3174,8 +4122,11 @@
       <c r="H14" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10">
       <c r="C15">
         <v>12</v>
       </c>
@@ -3191,8 +4142,11 @@
       <c r="H15" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10">
       <c r="C16">
         <v>13</v>
       </c>
@@ -3208,8 +4162,11 @@
       <c r="H16" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
       <c r="C17">
         <v>14</v>
       </c>
@@ -3225,8 +4182,11 @@
       <c r="H17" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10">
       <c r="C18">
         <v>15</v>
       </c>
@@ -3242,8 +4202,11 @@
       <c r="H18" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10">
       <c r="C19">
         <v>16</v>
       </c>
@@ -3259,8 +4222,11 @@
       <c r="H19" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
       <c r="C20">
         <v>17</v>
       </c>
@@ -3276,8 +4242,11 @@
       <c r="H20" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J20" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10">
       <c r="C21">
         <v>18</v>
       </c>
@@ -3293,8 +4262,11 @@
       <c r="H21" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10">
       <c r="C22">
         <v>19</v>
       </c>
@@ -3310,8 +4282,11 @@
       <c r="H22" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10">
       <c r="C23">
         <v>20</v>
       </c>
@@ -3327,8 +4302,11 @@
       <c r="H23" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10">
       <c r="C24">
         <v>21</v>
       </c>
@@ -3344,8 +4322,11 @@
       <c r="H24" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J24" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10">
       <c r="C25">
         <v>22</v>
       </c>
@@ -3361,8 +4342,11 @@
       <c r="H25" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J25" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10">
       <c r="C26">
         <v>23</v>
       </c>
@@ -3378,8 +4362,11 @@
       <c r="H26" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J26" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10">
       <c r="C27">
         <v>24</v>
       </c>
@@ -3395,8 +4382,11 @@
       <c r="H27" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J27" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10">
       <c r="C28">
         <v>25</v>
       </c>
@@ -3412,8 +4402,11 @@
       <c r="H28" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10">
       <c r="C29">
         <v>26</v>
       </c>
@@ -3429,8 +4422,11 @@
       <c r="H29" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J29" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10">
       <c r="C30">
         <v>27</v>
       </c>
@@ -3446,8 +4442,11 @@
       <c r="H30" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J30" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10">
       <c r="C31">
         <v>28</v>
       </c>
@@ -3463,8 +4462,11 @@
       <c r="H31" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J31" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10">
       <c r="C32">
         <v>29</v>
       </c>
@@ -3479,10 +4481,873 @@
       </c>
       <c r="H32" t="s">
         <v>442</v>
+      </c>
+      <c r="J32" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B7B707E-BC60-4FF0-A179-16E1E4003657}">
+  <dimension ref="B1:R35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="7" max="8" width="25.7109375" customWidth="1"/>
+    <col min="11" max="12" width="25.7109375" customWidth="1"/>
+    <col min="17" max="18" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18">
+      <c r="C1" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="2" spans="2:18">
+      <c r="C2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G2" t="s">
+        <v>352</v>
+      </c>
+      <c r="K2" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18">
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H4" t="s">
+        <v>536</v>
+      </c>
+      <c r="K4" t="s">
+        <v>567</v>
+      </c>
+      <c r="L4" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>627</v>
+      </c>
+      <c r="R4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>476</v>
+      </c>
+      <c r="G5" t="s">
+        <v>507</v>
+      </c>
+      <c r="H5" t="s">
+        <v>537</v>
+      </c>
+      <c r="K5" t="s">
+        <v>568</v>
+      </c>
+      <c r="L5" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>628</v>
+      </c>
+      <c r="R5" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>477</v>
+      </c>
+      <c r="G6" t="s">
+        <v>508</v>
+      </c>
+      <c r="H6" t="s">
+        <v>538</v>
+      </c>
+      <c r="K6" t="s">
+        <v>569</v>
+      </c>
+      <c r="L6" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>629</v>
+      </c>
+      <c r="R6" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G7" t="s">
+        <v>509</v>
+      </c>
+      <c r="H7" t="s">
+        <v>539</v>
+      </c>
+      <c r="K7" t="s">
+        <v>570</v>
+      </c>
+      <c r="L7" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>630</v>
+      </c>
+      <c r="R7" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>479</v>
+      </c>
+      <c r="G8" t="s">
+        <v>510</v>
+      </c>
+      <c r="H8" t="s">
+        <v>540</v>
+      </c>
+      <c r="K8" t="s">
+        <v>571</v>
+      </c>
+      <c r="L8" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>631</v>
+      </c>
+      <c r="R8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>480</v>
+      </c>
+      <c r="G9" t="s">
+        <v>511</v>
+      </c>
+      <c r="H9" t="s">
+        <v>541</v>
+      </c>
+      <c r="K9" t="s">
+        <v>572</v>
+      </c>
+      <c r="L9" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>632</v>
+      </c>
+      <c r="R9" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>481</v>
+      </c>
+      <c r="G10" t="s">
+        <v>512</v>
+      </c>
+      <c r="H10" t="s">
+        <v>542</v>
+      </c>
+      <c r="K10" t="s">
+        <v>573</v>
+      </c>
+      <c r="L10" t="s">
+        <v>603</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>633</v>
+      </c>
+      <c r="R10" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>482</v>
+      </c>
+      <c r="G11" t="s">
+        <v>513</v>
+      </c>
+      <c r="H11" t="s">
+        <v>543</v>
+      </c>
+      <c r="K11" t="s">
+        <v>574</v>
+      </c>
+      <c r="L11" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>634</v>
+      </c>
+      <c r="R11" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>483</v>
+      </c>
+      <c r="G12" t="s">
+        <v>514</v>
+      </c>
+      <c r="H12" t="s">
+        <v>544</v>
+      </c>
+      <c r="K12" t="s">
+        <v>575</v>
+      </c>
+      <c r="L12" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>635</v>
+      </c>
+      <c r="R12" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>484</v>
+      </c>
+      <c r="G13" t="s">
+        <v>515</v>
+      </c>
+      <c r="H13" t="s">
+        <v>545</v>
+      </c>
+      <c r="K13" t="s">
+        <v>576</v>
+      </c>
+      <c r="L13" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>636</v>
+      </c>
+      <c r="R13" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>485</v>
+      </c>
+      <c r="G14" t="s">
+        <v>516</v>
+      </c>
+      <c r="H14" t="s">
+        <v>546</v>
+      </c>
+      <c r="K14" t="s">
+        <v>577</v>
+      </c>
+      <c r="L14" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>637</v>
+      </c>
+      <c r="R14" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="45">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>486</v>
+      </c>
+      <c r="G15" t="s">
+        <v>517</v>
+      </c>
+      <c r="H15" t="s">
+        <v>547</v>
+      </c>
+      <c r="K15" t="s">
+        <v>578</v>
+      </c>
+      <c r="L15" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="R15" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>487</v>
+      </c>
+      <c r="G16" t="s">
+        <v>518</v>
+      </c>
+      <c r="H16" t="s">
+        <v>548</v>
+      </c>
+      <c r="K16" t="s">
+        <v>579</v>
+      </c>
+      <c r="L16" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>639</v>
+      </c>
+      <c r="R16" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>488</v>
+      </c>
+      <c r="G17" t="s">
+        <v>519</v>
+      </c>
+      <c r="H17" t="s">
+        <v>549</v>
+      </c>
+      <c r="K17" t="s">
+        <v>580</v>
+      </c>
+      <c r="L17" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>640</v>
+      </c>
+      <c r="R17" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>489</v>
+      </c>
+      <c r="G18" t="s">
+        <v>520</v>
+      </c>
+      <c r="H18" t="s">
+        <v>550</v>
+      </c>
+      <c r="K18" t="s">
+        <v>581</v>
+      </c>
+      <c r="L18" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>641</v>
+      </c>
+      <c r="R18" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>490</v>
+      </c>
+      <c r="G19" t="s">
+        <v>521</v>
+      </c>
+      <c r="H19" t="s">
+        <v>551</v>
+      </c>
+      <c r="K19" t="s">
+        <v>582</v>
+      </c>
+      <c r="L19" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>642</v>
+      </c>
+      <c r="R19" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>491</v>
+      </c>
+      <c r="G20" t="s">
+        <v>522</v>
+      </c>
+      <c r="H20" t="s">
+        <v>552</v>
+      </c>
+      <c r="K20" t="s">
+        <v>583</v>
+      </c>
+      <c r="L20" t="s">
+        <v>613</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>643</v>
+      </c>
+      <c r="R20" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>492</v>
+      </c>
+      <c r="G21" t="s">
+        <v>523</v>
+      </c>
+      <c r="H21" t="s">
+        <v>553</v>
+      </c>
+      <c r="K21" t="s">
+        <v>584</v>
+      </c>
+      <c r="L21" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>644</v>
+      </c>
+      <c r="R21" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>493</v>
+      </c>
+      <c r="G22" t="s">
+        <v>524</v>
+      </c>
+      <c r="H22" t="s">
+        <v>554</v>
+      </c>
+      <c r="K22" t="s">
+        <v>585</v>
+      </c>
+      <c r="L22" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>645</v>
+      </c>
+      <c r="R22" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>494</v>
+      </c>
+      <c r="G23" t="s">
+        <v>525</v>
+      </c>
+      <c r="H23" t="s">
+        <v>555</v>
+      </c>
+      <c r="K23" t="s">
+        <v>586</v>
+      </c>
+      <c r="L23" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>646</v>
+      </c>
+      <c r="R23" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>495</v>
+      </c>
+      <c r="G24" t="s">
+        <v>526</v>
+      </c>
+      <c r="H24" t="s">
+        <v>556</v>
+      </c>
+      <c r="K24" t="s">
+        <v>587</v>
+      </c>
+      <c r="L24" t="s">
+        <v>617</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>647</v>
+      </c>
+      <c r="R24" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>496</v>
+      </c>
+      <c r="G25" t="s">
+        <v>527</v>
+      </c>
+      <c r="H25" t="s">
+        <v>557</v>
+      </c>
+      <c r="K25" t="s">
+        <v>588</v>
+      </c>
+      <c r="L25" t="s">
+        <v>618</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>648</v>
+      </c>
+      <c r="R25" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>497</v>
+      </c>
+      <c r="G26" t="s">
+        <v>528</v>
+      </c>
+      <c r="H26" t="s">
+        <v>558</v>
+      </c>
+      <c r="K26" t="s">
+        <v>589</v>
+      </c>
+      <c r="L26" t="s">
+        <v>619</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>649</v>
+      </c>
+      <c r="R26" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>498</v>
+      </c>
+      <c r="G27" t="s">
+        <v>529</v>
+      </c>
+      <c r="H27" t="s">
+        <v>559</v>
+      </c>
+      <c r="K27" t="s">
+        <v>590</v>
+      </c>
+      <c r="L27" t="s">
+        <v>620</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>650</v>
+      </c>
+      <c r="R27" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="B28">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>499</v>
+      </c>
+      <c r="G28" t="s">
+        <v>530</v>
+      </c>
+      <c r="H28" t="s">
+        <v>560</v>
+      </c>
+      <c r="K28" t="s">
+        <v>591</v>
+      </c>
+      <c r="L28" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>651</v>
+      </c>
+      <c r="R28" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>500</v>
+      </c>
+      <c r="G29" t="s">
+        <v>531</v>
+      </c>
+      <c r="H29" t="s">
+        <v>561</v>
+      </c>
+      <c r="K29" t="s">
+        <v>592</v>
+      </c>
+      <c r="L29" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>652</v>
+      </c>
+      <c r="R29" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>501</v>
+      </c>
+      <c r="G30" t="s">
+        <v>532</v>
+      </c>
+      <c r="H30" t="s">
+        <v>562</v>
+      </c>
+      <c r="K30" t="s">
+        <v>593</v>
+      </c>
+      <c r="L30" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>653</v>
+      </c>
+      <c r="R30" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="B31">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>502</v>
+      </c>
+      <c r="G31" t="s">
+        <v>533</v>
+      </c>
+      <c r="H31" t="s">
+        <v>563</v>
+      </c>
+      <c r="K31" t="s">
+        <v>594</v>
+      </c>
+      <c r="L31" t="s">
+        <v>624</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>654</v>
+      </c>
+      <c r="R31" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="B32">
+        <v>28</v>
+      </c>
+      <c r="C32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G32" t="s">
+        <v>534</v>
+      </c>
+      <c r="H32" t="s">
+        <v>564</v>
+      </c>
+      <c r="K32" t="s">
+        <v>595</v>
+      </c>
+      <c r="L32" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>655</v>
+      </c>
+      <c r="R32" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
+      <c r="B33">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>504</v>
+      </c>
+      <c r="G33" t="s">
+        <v>535</v>
+      </c>
+      <c r="H33" t="s">
+        <v>565</v>
+      </c>
+      <c r="K33" t="s">
+        <v>596</v>
+      </c>
+      <c r="L33" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>656</v>
+      </c>
+      <c r="R33" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18">
+      <c r="Q34" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18">
+      <c r="Q35" t="s">
+        <v>658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>